--- a/pregenerated_results/ate_evalue_survey.xlsx
+++ b/pregenerated_results/ate_evalue_survey.xlsx
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4740212656916218</v>
+        <v>0.4677085962881639</v>
       </c>
       <c r="D2" t="n">
-        <v>1.539348618242923</v>
+        <v>1.530531135613223</v>
       </c>
       <c r="E2" t="n">
-        <v>2.450526729395442</v>
+        <v>2.431638466328205</v>
       </c>
       <c r="F2" t="n">
-        <v>2.013998684568712</v>
+        <v>2.176386862865465</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -510,11 +510,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E-value = 2.45. An unmeasured confounder would need risk ratio associations of at least 2.45 with both treatment and outcome to explain away this effect. This represents moderate robustness. The E-value for the confidence interval bound is 2.01, meaning a confounder of this strength could shift the CI to include the null.</t>
+          <t>E-value = 2.43. An unmeasured confounder would need risk ratio associations of at least 2.43 with both treatment and outcome to explain away this effect. This represents moderate robustness. The E-value for the confidence interval bound is 2.18, meaning a confounder of this strength could shift the CI to include the null. For continuous outcomes, E-value uses an approximate RR conversion; interpretation is approximate.</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.645104327879733e-24</v>
+        <v>4.032349524444037e-24</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.06073443341649937</v>
+        <v>-0.06413795733398037</v>
       </c>
       <c r="D3" t="n">
-        <v>1.05682415891757</v>
+        <v>1.060102435982214</v>
       </c>
       <c r="E3" t="n">
-        <v>1.301881588827906</v>
+        <v>1.312520222188358</v>
       </c>
       <c r="F3" t="n">
-        <v>1.483182073263504</v>
+        <v>1.507842685559293</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,11 +550,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>E-value = 1.30. This effect is highly sensitive to unmeasured confounding and could easily be explained by a weak confounder. The E-value for the confidence interval bound is 1.48, meaning a confounder of this strength could shift the CI to include the null.</t>
+          <t>E-value = 1.31. This effect is highly sensitive to unmeasured confounding and could easily be explained by a weak confounder. The E-value for the confidence interval bound is 1.51, meaning a confounder of this strength could shift the CI to include the null. For continuous outcomes, E-value uses an approximate RR conversion; interpretation is approximate.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.3360117637295972</v>
+        <v>0.3345692469681957</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2684816016281894</v>
+        <v>0.2528818070312245</v>
       </c>
       <c r="D4" t="n">
-        <v>1.276750601267726</v>
+        <v>1.258754127885786</v>
       </c>
       <c r="E4" t="n">
-        <v>1.871175951139157</v>
+        <v>1.829462307767342</v>
       </c>
       <c r="F4" t="n">
-        <v>1.545535761361446</v>
+        <v>1.567505295039366</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -590,11 +590,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>E-value = 1.87. A relatively weak unmeasured confounder (RR ≈ 1.87) could potentially explain this effect. Interpret with caution. The E-value for the confidence interval bound is 1.55, meaning a confounder of this strength could shift the CI to include the null.</t>
+          <t>E-value = 1.83. A relatively weak unmeasured confounder (RR ≈ 1.83) could potentially explain this effect. Interpret with caution. The E-value for the confidence interval bound is 1.57, meaning a confounder of this strength could shift the CI to include the null. For continuous outcomes, E-value uses an approximate RR conversion; interpretation is approximate.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.453607464503609e-08</v>
+        <v>7.096210791271912e-08</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
